--- a/templates/04_nutricao/09_ficha_antropometrica.xlsx
+++ b/templates/04_nutricao/09_ficha_antropometrica.xlsx
@@ -4,22 +4,77 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Ficha_Antropometrica" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Avaliação" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Composição Corporal" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Medida</t>
-  </si>
-  <si>
-    <t>Observação</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="21">
+  <si>
+    <t>Medida (cm)</t>
+  </si>
+  <si>
+    <t>Atual</t>
+  </si>
+  <si>
+    <t>Anterior</t>
+  </si>
+  <si>
+    <t>Diferença</t>
+  </si>
+  <si>
+    <t>Tórax (cm)</t>
+  </si>
+  <si>
+    <t>[ ]</t>
+  </si>
+  <si>
+    <t>[FÓRMULA: B-C]</t>
+  </si>
+  <si>
+    <t>Braço Direito (cm)</t>
+  </si>
+  <si>
+    <t>Braço Esquerdo (cm)</t>
+  </si>
+  <si>
+    <t>Cintura (cm)</t>
+  </si>
+  <si>
+    <t>Abdômen (cm)</t>
+  </si>
+  <si>
+    <t>Quadril (cm)</t>
+  </si>
+  <si>
+    <t>Coxa Direita (cm)</t>
+  </si>
+  <si>
+    <t>Parâmetro</t>
+  </si>
+  <si>
+    <t>Valor (%)</t>
+  </si>
+  <si>
+    <t>Classificação</t>
+  </si>
+  <si>
+    <t>Gordura (%)</t>
+  </si>
+  <si>
+    <t>Massa Magra (%)</t>
+  </si>
+  <si>
+    <t>Peso (kg)</t>
+  </si>
+  <si>
+    <t>IMC</t>
+  </si>
+  <si>
+    <t>[FÓRMULA: PESO / ALTURA^2]</t>
   </si>
 </sst>
 </file>
@@ -37,7 +92,6 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -67,9 +121,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -409,18 +461,191 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="4" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="3" width="20" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
